--- a/Test-Sample.xlsx
+++ b/Test-Sample.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amarreddy/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amarreddy/Documents/GitHub/MyDevFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54509610-FAE6-6147-A79B-5D422424D0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACD6052-1BC1-2D43-A8E2-C8B2795F3B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="520" windowWidth="25600" windowHeight="14380" xr2:uid="{D921019B-E8E2-F14C-BE89-55F43F38C0DE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14380" xr2:uid="{D921019B-E8E2-F14C-BE89-55F43F38C0DE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Q vs A_Citigroup" sheetId="3" r:id="rId1"/>
-    <sheet name="Across Cycles_Citigroup" sheetId="2" r:id="rId2"/>
+    <sheet name="Across Cycles_Citigroup" sheetId="2" r:id="rId1"/>
+    <sheet name="Q vs A_Citigroup" sheetId="3" r:id="rId2"/>
     <sheet name="Across Scenario_Citigroup" sheetId="4" r:id="rId3"/>
     <sheet name="Q vs A_CBNA" sheetId="5" r:id="rId4"/>
     <sheet name="Across Cycles_CBNA" sheetId="6" r:id="rId5"/>
@@ -402,11 +402,42 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="5" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="5" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -423,45 +454,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="5" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="40% - Accent4" xfId="4" builtinId="43"/>
@@ -807,12 +805,181 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{659145F6-170D-A245-B478-D81CBC588516}">
+  <dimension ref="A1:Y5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="3" max="3" width="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5" customWidth="1"/>
+    <col min="24" max="24" width="23.83203125" customWidth="1"/>
+    <col min="25" max="25" width="25.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="3" spans="1:25" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="18"/>
+      <c r="Y3" s="18"/>
+    </row>
+    <row r="4" spans="1:25" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y4" s="24"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="V5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="W5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="D3:Y3"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="N4:W4"/>
+    <mergeCell ref="X4:Y4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0D90F65-2435-C349-86FB-C80B2B16D9A8}">
   <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="4" max="4" width="1.33203125" style="16" customWidth="1"/>
+    <col min="4" max="4" width="1.33203125" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="14" max="14" width="1.33203125" customWidth="1"/>
@@ -822,66 +989,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="Y2" s="17" t="s">
+      <c r="Y2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="18"/>
-      <c r="AB2" s="17" t="s">
+      <c r="Z2" s="14"/>
+      <c r="AB2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="AC2" s="18"/>
+      <c r="AC2" s="14"/>
     </row>
     <row r="3" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="12" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="14"/>
-      <c r="O3" s="12" t="s">
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="12"/>
+      <c r="O3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="14"/>
-      <c r="Y3" s="20" t="s">
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="12"/>
+      <c r="Y3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="Z3" s="21"/>
-      <c r="AB3" s="20" t="s">
+      <c r="Z3" s="16"/>
+      <c r="AB3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AC3" s="21"/>
+      <c r="AC3" s="16"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="E4" t="s">
         <v>3</v>
       </c>
@@ -951,184 +1118,17 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="AB3:AC3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E3:M3"/>
     <mergeCell ref="O3:W3"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="AB3:AC3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{659145F6-170D-A245-B478-D81CBC588516}">
-  <dimension ref="A1:Y5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="1" customWidth="1"/>
-    <col min="24" max="24" width="28.6640625" customWidth="1"/>
-    <col min="25" max="25" width="35" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:25" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="3" spans="1:25" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
-    </row>
-    <row r="4" spans="1:25" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y4" s="9"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="N5" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P5" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="R5" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="S5" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="T5" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="U5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="V5" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="W5" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="X5" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="D3:Y3"/>
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="N4:W4"/>
-    <mergeCell ref="X4:Y4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1148,54 +1148,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="16"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:27" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="12" t="s">
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="26"/>
+      <c r="O2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="27"/>
-      <c r="Z2" s="12" t="s">
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="26"/>
+      <c r="Z2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AA2" s="14"/>
+      <c r="AA2" s="12"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="16"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="D3" t="s">
         <v>3</v>
       </c>
@@ -1256,10 +1253,10 @@
       <c r="X3" t="s">
         <v>25</v>
       </c>
-      <c r="Z3" s="28" t="s">
+      <c r="Z3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AA3" s="28" t="s">
+      <c r="AA3" s="7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1282,7 +1279,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="4" max="4" width="1.33203125" style="16" customWidth="1"/>
+    <col min="4" max="4" width="1.33203125" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="14" max="14" width="1.33203125" customWidth="1"/>
@@ -1292,66 +1289,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="Y2" s="17" t="s">
+      <c r="Y2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="18"/>
-      <c r="AB2" s="17" t="s">
+      <c r="Z2" s="14"/>
+      <c r="AB2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="AC2" s="18"/>
+      <c r="AC2" s="14"/>
     </row>
     <row r="3" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="12" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="14"/>
-      <c r="O3" s="12" t="s">
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="12"/>
+      <c r="O3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="14"/>
-      <c r="Y3" s="20" t="s">
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="12"/>
+      <c r="Y3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="Z3" s="21"/>
-      <c r="AB3" s="20" t="s">
+      <c r="Z3" s="16"/>
+      <c r="AB3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AC3" s="21"/>
+      <c r="AC3" s="16"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="E4" t="s">
         <v>3</v>
       </c>
@@ -1453,139 +1450,139 @@
       <c r="C1" s="2"/>
     </row>
     <row r="3" spans="1:25" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="18"/>
+      <c r="Y3" s="18"/>
     </row>
     <row r="4" spans="1:25" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="4" t="s">
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="8" t="s">
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="Y4" s="9"/>
+      <c r="Y4" s="24"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="23" t="s">
+      <c r="L5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="M5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="23" t="s">
+      <c r="N5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="O5" s="23" t="s">
+      <c r="O5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="P5" s="23" t="s">
+      <c r="P5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="Q5" s="23" t="s">
+      <c r="Q5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="23" t="s">
+      <c r="R5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="S5" s="23" t="s">
+      <c r="S5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="T5" s="23" t="s">
+      <c r="T5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="23" t="s">
+      <c r="U5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="V5" s="23" t="s">
+      <c r="V5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="W5" s="23" t="s">
+      <c r="W5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="X5" s="23" t="s">
+      <c r="X5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Y5" s="23" t="s">
+      <c r="Y5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1617,54 +1614,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="16"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:27" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="12" t="s">
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="26"/>
+      <c r="O2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="27"/>
-      <c r="Z2" s="12" t="s">
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="26"/>
+      <c r="Z2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AA2" s="14"/>
+      <c r="AA2" s="12"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="16"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="D3" t="s">
         <v>3</v>
       </c>
@@ -1725,21 +1719,21 @@
       <c r="X3" t="s">
         <v>25</v>
       </c>
-      <c r="Z3" s="28" t="s">
+      <c r="Z3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AA3" s="28" t="s">
+      <c r="AA3" s="7" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="Z2:AA2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="D2:M2"/>
     <mergeCell ref="O2:X2"/>
-    <mergeCell ref="Z2:AA2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
